--- a/media/exports/reports/2026-04/growth.xlsx
+++ b/media/exports/reports/2026-04/growth.xlsx
@@ -30,50 +30,60 @@
     <numFmt numFmtId="164" formatCode="#,##0;[Red](#,##0);&quot;-&quot;"/>
     <numFmt numFmtId="165" formatCode="0.0%;[Red](0.0%);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="13"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
   </fonts>
@@ -105,35 +115,35 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1498,8 +1508,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -3172,8 +3182,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5629,8 +5639,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -5808,8 +5818,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8256,8 +8266,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -8435,8 +8445,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 SME sample businesses&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 growth.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 SME sample businesses&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 growth.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/reports/2026-04/growth.xlsx
+++ b/media/exports/reports/2026-04/growth.xlsx
@@ -683,10 +683,10 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, the most profitable work you do. Installations: 28.4% gross margin, below the 39.8% needed to cover overheads.</t>
+          <t>Installations: 28.4% gross margin, 6.6 points under the 35.0% target: about $66,763 on $1,011,500 of revenue this financial year to date. It's below the 39.8% needed to cover overheads, too. Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($87,069 ahead on $355,300 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
     <row r="36" ht="30" customHeight="1">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>Maintenance contracts: 59.5% gross margin, 19.7 points clear of the 39.8% overheads need.</t>
+          <t>Maintenance contracts: 59.5% gross margin, 24.5 points over the 35.0% target ($87,069 ahead on $355,300 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -889,10 +889,10 @@
         </is>
       </c>
     </row>
-    <row r="48" ht="30" customHeight="1">
+    <row r="48" ht="45" customHeight="1">
       <c r="A48" s="3" t="inlineStr">
         <is>
-          <t>Installations: 28.4% gross margin, below the 39.8% needed to cover overheads.</t>
+          <t>Installations: 28.4% gross margin, 6.6 points under the 35.0% target: about $66,763 on $1,011,500 of revenue this financial year to date. It's below the 39.8% needed to cover overheads, too.</t>
         </is>
       </c>
     </row>
@@ -995,7 +995,7 @@
     <row r="60" ht="30" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>Call-outs and repairs: 43.7% gross margin, 3.8 points clear of the 39.8% overheads need.</t>
+          <t>Call-outs and repairs: 43.7% gross margin, 8.7 points over the 35.0% target ($21,176 ahead on $243,781 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1147,10 +1147,10 @@
         </is>
       </c>
     </row>
-    <row r="82" ht="30" customHeight="1">
+    <row r="82" ht="45" customHeight="1">
       <c r="A82" s="3" t="inlineStr">
         <is>
-          <t>Training: 74.6% gross margin, the most profitable work you do. Projects: 61.6% gross margin, below the 88.6% needed to cover overheads.</t>
+          <t>Projects: 61.6% gross margin, 21.6 points over the 40.0% target ($109,938 ahead on $509,230 this financial year to date). Training: 74.6% gross margin, 34.6 points over the 40.0% target ($24,420 ahead on $70,600 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1253,7 +1253,7 @@
     <row r="94" ht="30" customHeight="1">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Projects: 61.6% gross margin, below the 88.6% needed to cover overheads.</t>
+          <t>Projects: 61.6% gross margin, 21.6 points over the 40.0% target ($109,938 ahead on $509,230 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1356,7 +1356,7 @@
     <row r="106" ht="30" customHeight="1">
       <c r="A106" s="3" t="inlineStr">
         <is>
-          <t>Retainers: 66.0% gross margin, below the 88.6% needed to cover overheads.</t>
+          <t>Retainers: 66.0% gross margin, 26.0 points over the 40.0% target ($61,200 ahead on $235,000 this financial year to date).</t>
         </is>
       </c>
     </row>
@@ -1459,7 +1459,7 @@
     <row r="118" ht="30" customHeight="1">
       <c r="A118" s="3" t="inlineStr">
         <is>
-          <t>Training: 74.6% gross margin, below the 88.6% needed to cover overheads.</t>
+          <t>Training: 74.6% gross margin, 34.6 points over the 40.0% target ($24,420 ahead on $70,600 this financial year to date).</t>
         </is>
       </c>
     </row>

--- a/media/exports/reports/2026-04/growth.xlsx
+++ b/media/exports/reports/2026-04/growth.xlsx
@@ -15,10 +15,40 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Year to date Services" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="Trades_April_against_April_last_year">'Report'!$B$16</definedName>
+    <definedName name="Trades_Year_to_date_Jul_to_Apr_2026">'Report'!$B$17</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date">'Report'!$B$18</definedName>
+    <definedName name="Trades_April_against_April_last_year_2">'Report'!$B$28</definedName>
+    <definedName name="Trades_Year_to_date_Jul_to_Apr_2026_2">'Report'!$B$29</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date_2">'Report'!$B$30</definedName>
+    <definedName name="Trades_April_against_April_last_year_3">'Report'!$B$40</definedName>
+    <definedName name="Trades_Year_to_date_Jul_to_Apr_2026_3">'Report'!$B$41</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date_3">'Report'!$B$42</definedName>
+    <definedName name="Trades_April_against_April_last_year_4">'Report'!$B$52</definedName>
+    <definedName name="Trades_Year_to_date_Jul_to_Apr_2026_4">'Report'!$B$53</definedName>
+    <definedName name="Trades_Gross_margin_year_to_date_4">'Report'!$B$54</definedName>
+    <definedName name="Services_April_against_April_last_year">'Report'!$B$74</definedName>
+    <definedName name="Services_Year_to_date_Jul_to_Apr_2026">'Report'!$B$75</definedName>
+    <definedName name="Services_Gross_margin_year_to_date">'Report'!$B$76</definedName>
+    <definedName name="Services_April_against_April_last_year_2">'Report'!$B$86</definedName>
+    <definedName name="Services_Year_to_date_Jul_to_Apr_2026_2">'Report'!$B$87</definedName>
+    <definedName name="Services_Gross_margin_year_to_date_2">'Report'!$B$88</definedName>
+    <definedName name="Services_April_against_April_last_year_3">'Report'!$B$98</definedName>
+    <definedName name="Services_Year_to_date_Jul_to_Apr_2026_3">'Report'!$B$99</definedName>
+    <definedName name="Services_Gross_margin_year_to_date_3">'Report'!$B$100</definedName>
+    <definedName name="Services_April_against_April_last_year_4">'Report'!$B$110</definedName>
+    <definedName name="Services_Year_to_date_Jul_to_Apr_2026_4">'Report'!$B$111</definedName>
+    <definedName name="Services_Gross_margin_year_to_date_4">'Report'!$B$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'Report'!$A$1:$D$121</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'Workings'!$A$1:$B$228</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Data Trades'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Data Trades'!$A$1:$G$81</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Year to date Trades'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Year to date Trades'!$A$1:$F$9</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Data Services'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Data Services'!$A$1:$G$81</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Year to date Services'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Year to date Services'!$A$1:$F$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -61,11 +91,6 @@
       <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
-    </font>
-    <font>
-      <name val="Roboto"/>
-      <b val="1"/>
-      <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
@@ -81,6 +106,11 @@
     <font>
       <name val="Roboto"/>
       <b val="1"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
+      <b val="1"/>
+      <color rgb="002F7A5D"/>
     </font>
     <font>
       <name val="Roboto"/>
@@ -125,25 +155,27 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -221,6 +253,538 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$6:$D$24</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Maintenance contracts</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$25:$D$43</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Installations</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$44:$D$62</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Call-outs and repairs</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Trades'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Trades'!$D$63:$D$81</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="2"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr sz="1100" b="1">
+                <a:solidFill>
+                  <a:srgbClr val="25342A"/>
+                </a:solidFill>
+                <a:latin typeface="Roboto"/>
+              </a:rPr>
+              <a:t>Revenue by month</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+      <overlay val="0"/>
+    </title>
+    <plotArea>
+      <lineChart>
+        <grouping val="standard"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>All</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="0E9F6E"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$6:$D$24</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Projects</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="2F7A5D"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$25:$D$43</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <v>Retainers</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="8A6D3B"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$44:$D$62</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <v>Training</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="22000">
+              <a:solidFill>
+                <a:srgbClr val="5F6F63"/>
+              </a:solidFill>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <cat>
+            <numRef>
+              <f>'Data Services'!$B$6:$B$24</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Data Services'!$D$63:$D$81</f>
+            </numRef>
+          </val>
+          <smooth val="0"/>
+        </ser>
+        <axId val="10"/>
+        <axId val="100"/>
+      </lineChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <numFmt formatCode="@" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+        <tickLblSkip val="1"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <numFmt formatCode="#,##0;(#,##0)" sourceLinked="0"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>8</col>
+      <colOff>0</colOff>
+      <row>4</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="2880000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="growth_Data_Trades" displayName="growth_Data_Trades" ref="A5:G81" headerRowCount="1">
+  <autoFilter ref="A5:G81"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="growth_Year_to_date_Trades" displayName="growth_Year_to_date_Trades" ref="A5:F9" headerRowCount="1">
+  <autoFilter ref="A5:F9"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Year to date"/>
+    <tableColumn id="3" name="Same period last year"/>
+    <tableColumn id="4" name="Growth"/>
+    <tableColumn id="5" name="Gross margin $"/>
+    <tableColumn id="6" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="growth_Data_Services" displayName="growth_Data_Services" ref="A5:G81" headerRowCount="1">
+  <autoFilter ref="A5:G81"/>
+  <tableColumns count="7">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Month"/>
+    <tableColumn id="3" name="Status"/>
+    <tableColumn id="4" name="Revenue"/>
+    <tableColumn id="5" name="Direct cost"/>
+    <tableColumn id="6" name="Gross margin"/>
+    <tableColumn id="7" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="growth_Year_to_date_Services" displayName="growth_Year_to_date_Services" ref="A5:F9" headerRowCount="1">
+  <autoFilter ref="A5:F9"/>
+  <tableColumns count="6">
+    <tableColumn id="1" name="Line"/>
+    <tableColumn id="2" name="Year to date"/>
+    <tableColumn id="3" name="Same period last year"/>
+    <tableColumn id="4" name="Growth"/>
+    <tableColumn id="5" name="Gross margin $"/>
+    <tableColumn id="6" name="Gross margin %"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -531,7 +1095,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -561,14 +1125,14 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>April's jobs made $68,843 gross margin (41.7%). Technician time not charged to jobs took $6,456 and overheads $59,290, leaving $3,097 profit before tax (1.9% of revenue). To cover overheads, jobs need a 39.8% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -576,14 +1140,14 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="3" t="inlineStr">
         <is>
-          <t>April's jobs made $68,843 gross margin (41.7%). Technician time not charged to jobs took $6,456 and overheads $59,290, leaving $3,097 profit before tax (1.9% of revenue). To cover overheads, jobs need a 39.8% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Job gross margin = revenue less materials, subcontractors and technician time charged to the job at $68 an hour (wages and all on-costs). Not included: technician time not charged to any job (travel, training, waiting), and overheads (office wages, marketing, vehicles, rent, insurance, IT, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -1025,14 +1589,14 @@
     <row r="66">
       <c r="A66" s="5" t="inlineStr">
         <is>
-          <t>Gross margin, not profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="75" customHeight="1">
+          <t>From gross margin to profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="60" customHeight="1">
       <c r="A67" s="3" t="inlineStr">
         <is>
-          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
+          <t>April's client work made $52,730 gross margin (65.4%). Consultant time not charged to client work took $19,740 and overheads $51,660, leaving ($18,670) profit before tax ((23.2%) of revenue). To cover overheads, client work needs a 88.6% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
         </is>
       </c>
     </row>
@@ -1040,14 +1604,14 @@
     <row r="69">
       <c r="A69" s="5" t="inlineStr">
         <is>
-          <t>From gross margin to profit</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
+          <t>Gross margin, not profit</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="75" customHeight="1">
       <c r="A70" s="3" t="inlineStr">
         <is>
-          <t>April's client work made $52,730 gross margin (65.4%). Consultant time not charged to client work took $19,740 and overheads $51,660, leaving ($18,670) profit before tax ((23.2%) of revenue). To cover overheads, client work needs a 88.6% gross margin on average. (Workings sheet: "From gross margin to profit".)</t>
+          <t>Gross margin is not profit. Gross margin = revenue less contractors and consultant time charged to the work at $60 an hour (wages and all on-costs). Not included: consultant time not charged to clients, and overheads (management and admin wages, marketing, rent, IT, insurance, travel, depreciation, interest). Profit is what's left after those. Wages always include all on-costs: super, payroll tax, workers' compensation insurance and leave.</t>
         </is>
       </c>
     </row>
@@ -1550,7 +2114,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -3229,7 +3793,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -5651,6 +6215,10 @@
     <brk id="43" min="0" max="16383" man="1"/>
     <brk id="62" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5681,7 +6249,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -5825,6 +6393,9 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5856,7 +6427,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -8278,6 +8849,10 @@
     <brk id="43" min="0" max="16383" man="1"/>
     <brk id="62" min="0" max="16383" man="1"/>
   </rowBreaks>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -8308,7 +8883,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet</t>
+          <t>SME sample businesses · SAMPLE DATA (invented) · The Fourth Sheet · Made with Python (openpyxl)</t>
         </is>
       </c>
     </row>
@@ -8452,5 +9027,8 @@
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
+  <tableParts count="1">
+    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </tableParts>
 </worksheet>
 </file>